--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.79855549245997</v>
+        <v>9.229765267524746</v>
       </c>
       <c r="D2" t="n">
-        <v>57.55835031036145</v>
+        <v>9.353231925433736</v>
       </c>
       <c r="E2" t="n">
-        <v>17.90258420183261</v>
+        <v>2.9091699327978</v>
       </c>
       <c r="F2" t="n">
-        <v>18.25343796811849</v>
+        <v>2.966183669819255</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.80947321165661</v>
+        <v>3.381539396894199</v>
       </c>
       <c r="D3" t="n">
-        <v>20.04310551746238</v>
+        <v>3.257004646587636</v>
       </c>
       <c r="E3" t="n">
-        <v>17.90258420183261</v>
+        <v>2.9091699327978</v>
       </c>
       <c r="F3" t="n">
-        <v>18.25343796811849</v>
+        <v>2.966183669819255</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.5031113933145</v>
+        <v>9.831755601413606</v>
       </c>
       <c r="D4" t="n">
-        <v>17.7341478509682</v>
+        <v>2.881799025782332</v>
       </c>
       <c r="E4" t="n">
-        <v>17.90258420183261</v>
+        <v>2.9091699327978</v>
       </c>
       <c r="F4" t="n">
-        <v>18.25343796811849</v>
+        <v>2.966183669819255</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
